--- a/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-pothole_tiny_3.xlsx
+++ b/tests/perf_v2/perf_history/v2.5/detection/DETECTION-raw-pothole_tiny_3.xlsx
@@ -7,15 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_resnext101" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dfine_x" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_101" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtdetr_50" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ssd_mobilenetv2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_l" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="atss_mobilenetv2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rtmdet_tiny" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_s" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_tiny" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yolox_x" sheetId="12" state="visible" r:id="rId12"/>
@@ -596,56 +596,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>28.23449778556824</v>
+        <v>103.7587566375732</v>
       </c>
       <c r="D2" t="n">
-        <v>6.460000038146973</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1421160864479401</v>
+        <v>0.4705673364960417</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5333333611488342</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2952381074428558</v>
+        <v>0.2835820913314819</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1167883202433586</v>
+        <v>0.1176470592617988</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1142857149243354</v>
+        <v>0.1014492735266685</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1073194816708564</v>
+        <v>0.1797310709953308</v>
       </c>
       <c r="K2" t="n">
-        <v>13.46582937240601</v>
+        <v>55.34845972061157</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0367176055908203</v>
+        <v>0.08723621845245361</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0684329557418823</v>
+        <v>0.4610617160797119</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0857119083404541</v>
+        <v>0.1702107572555542</v>
       </c>
       <c r="O2" t="n">
-        <v>1.835880279541016</v>
+        <v>4.361810922622681</v>
       </c>
       <c r="P2" t="n">
-        <v>3.421647787094116</v>
+        <v>23.0530858039856</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.285595417022705</v>
+        <v>8.51053786277771</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250627-154332</t>
+          <t>20250725-215656</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -670,22 +670,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -717,56 +717,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>54.53179097175598</v>
+        <v>125.7311344146728</v>
       </c>
       <c r="D3" t="n">
-        <v>6.480000019073486</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1453837430563526</v>
+        <v>0.4685197775646791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4545454680919647</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3453237414360046</v>
+        <v>0.4480874240398407</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1702127605676651</v>
+        <v>0.4480874240398407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1702127605676651</v>
+        <v>0.437158465385437</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1033629700541496</v>
+        <v>0.1774202287197113</v>
       </c>
       <c r="K3" t="n">
-        <v>19.05455040931702</v>
+        <v>54.3113374710083</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0341227149963378</v>
+        <v>0.0753162240982055</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0746825742721557</v>
+        <v>0.4599117755889892</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0817127323150634</v>
+        <v>0.1697351646423339</v>
       </c>
       <c r="O3" t="n">
-        <v>1.706135749816894</v>
+        <v>3.765811204910278</v>
       </c>
       <c r="P3" t="n">
-        <v>3.734128713607788</v>
+        <v>22.99558877944946</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.085636615753174</v>
+        <v>8.486758232116699</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250627-154458</t>
+          <t>20250725-220059</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -791,22 +791,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,56 +838,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
-        <v>35.30303716659546</v>
+        <v>53.71024560928345</v>
       </c>
       <c r="D4" t="n">
-        <v>6.460000038146973</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.145390549166636</v>
+        <v>0.4683452881872654</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4064171016216278</v>
+        <v>0.2790697813034057</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4064171016216278</v>
+        <v>0.1142857149243354</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3777777850627899</v>
+        <v>0.1267605572938919</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1012242883443832</v>
+        <v>0.1831370592117309</v>
       </c>
       <c r="K4" t="n">
-        <v>13.69968914985657</v>
+        <v>49.39689064025879</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0343540620803833</v>
+        <v>0.08154605865478511</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0705648183822631</v>
+        <v>0.460198974609375</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0880775594711303</v>
+        <v>0.1635592174530029</v>
       </c>
       <c r="O4" t="n">
-        <v>1.717703104019165</v>
+        <v>4.077302932739258</v>
       </c>
       <c r="P4" t="n">
-        <v>3.528240919113159</v>
+        <v>23.00994873046875</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.403877973556519</v>
+        <v>8.177960872650146</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250627-154700</t>
+          <t>20250725-220524</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -962,53 +962,53 @@
         <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>24.30372500419617</v>
+        <v>63.07940578460693</v>
       </c>
       <c r="D5" t="n">
-        <v>6.480000019073486</v>
+        <v>15.40999984741211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1450734102520449</v>
+        <v>0.4680760163685371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.4210526347160339</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2285714298486709</v>
+        <v>0.4347825944423675</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1678321659564972</v>
+        <v>0.437158465385437</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1655172407627105</v>
+        <v>0.4153005480766296</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1123669892549514</v>
+        <v>0.1762770414352417</v>
       </c>
       <c r="K5" t="n">
-        <v>13.50382041931152</v>
+        <v>54.5660879611969</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0391898775100708</v>
+        <v>0.0780398321151733</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06975539684295649</v>
+        <v>0.4605835103988647</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0855686616897583</v>
+        <v>0.1719052648544311</v>
       </c>
       <c r="O5" t="n">
-        <v>1.95949387550354</v>
+        <v>3.901991605758667</v>
       </c>
       <c r="P5" t="n">
-        <v>3.487769842147827</v>
+        <v>23.02917551994324</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.278433084487915</v>
+        <v>8.595263242721558</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250627-154833</t>
+          <t>20250725-220831</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1080,56 +1080,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
-        <v>48.95585107803345</v>
+        <v>106.8188281059265</v>
       </c>
       <c r="D6" t="n">
-        <v>6.460000038146973</v>
+        <v>15.4399995803833</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1430299766361712</v>
+        <v>0.4690981361330772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5555555820465088</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4036697149276733</v>
+        <v>0.3655914068222046</v>
       </c>
       <c r="H6" t="n">
-        <v>0.409090906381607</v>
+        <v>0.3125</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3856502175331116</v>
+        <v>0.3125</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1071620285511016</v>
+        <v>0.1804837733507156</v>
       </c>
       <c r="K6" t="n">
-        <v>13.50362253189087</v>
+        <v>54.82697939872742</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0353055238723754</v>
+        <v>0.08011342048645009</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0782226800918579</v>
+        <v>0.45721923828125</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0870033740997314</v>
+        <v>0.1756143140792846</v>
       </c>
       <c r="O6" t="n">
-        <v>1.765276193618774</v>
+        <v>4.00567102432251</v>
       </c>
       <c r="P6" t="n">
-        <v>3.911134004592896</v>
+        <v>22.8609619140625</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.350168704986572</v>
+        <v>8.780715703964233</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250627-154955</t>
+          <t>20250725-221142</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_mobilenetv2</t>
+          <t>atss_resnext101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1154,22 +1154,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3680,56 +3680,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C2" t="n">
-        <v>58.17530703544617</v>
+        <v>235.3326721191407</v>
       </c>
       <c r="D2" t="n">
-        <v>9.770000457763672</v>
+        <v>20.63999938964844</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2876753158429089</v>
+        <v>0.5431680518095611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.5882353186607361</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4188481569290161</v>
+        <v>0.4362139999866485</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2222222238779068</v>
+        <v>0.3978494703769684</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1971831023693084</v>
+        <v>0.402010053396225</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1284314095973968</v>
+        <v>0.1444242894649505</v>
       </c>
       <c r="K2" t="n">
-        <v>71.22571706771851</v>
+        <v>81.43808007240295</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0863721179962158</v>
+        <v>0.0676279401779174</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4593184614181518</v>
+        <v>0.1985846042633056</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1736040449142456</v>
+        <v>0.1963083362579345</v>
       </c>
       <c r="O2" t="n">
-        <v>4.318605899810791</v>
+        <v>3.381397008895874</v>
       </c>
       <c r="P2" t="n">
-        <v>22.9659230709076</v>
+        <v>9.929230213165283</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.68020224571228</v>
+        <v>9.815416812896729</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250629-052312</t>
+          <t>20250724-135629</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -3754,22 +3754,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -3801,56 +3801,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C3" t="n">
-        <v>50.48340916633606</v>
+        <v>262.0190901756287</v>
       </c>
       <c r="D3" t="n">
-        <v>9.739999771118164</v>
+        <v>20.81999969482422</v>
       </c>
       <c r="E3" t="n">
-        <v>0.286826622897181</v>
+        <v>0.514296636633251</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3199999928474426</v>
+        <v>0.4927536249160766</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1549295783042907</v>
+        <v>0.4859813153743744</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1549295783042907</v>
+        <v>0.4761904776096344</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1335913985967636</v>
+        <v>0.1517852246761322</v>
       </c>
       <c r="K3" t="n">
-        <v>74.83589506149292</v>
+        <v>81.03132081031799</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08760747909545891</v>
+        <v>0.07378224372863761</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4610066890716552</v>
+        <v>0.2056029319763183</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1708809375762939</v>
+        <v>0.1972367286682129</v>
       </c>
       <c r="O3" t="n">
-        <v>4.380373954772949</v>
+        <v>3.689112186431885</v>
       </c>
       <c r="P3" t="n">
-        <v>23.05033445358276</v>
+        <v>10.28014659881592</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.544046878814697</v>
+        <v>9.861836433410645</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250629-052648</t>
+          <t>20250724-140314</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -3875,22 +3875,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -3922,56 +3922,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C4" t="n">
-        <v>58.71019601821899</v>
+        <v>249.6767358779907</v>
       </c>
       <c r="D4" t="n">
-        <v>9.770000457763672</v>
+        <v>21.14999961853028</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2862523408497081</v>
+        <v>0.5199140332528015</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.7058823704719543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4022346436977386</v>
+        <v>0.5514018535614014</v>
       </c>
       <c r="H4" t="n">
-        <v>0.251655638217926</v>
+        <v>0.5130890011787415</v>
       </c>
       <c r="I4" t="n">
-        <v>0.264900654554367</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1287539303302765</v>
+        <v>0.1394746154546737</v>
       </c>
       <c r="K4" t="n">
-        <v>73.75497341156006</v>
+        <v>74.37973237037659</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0865830659866333</v>
+        <v>0.0702948474884033</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4587494850158691</v>
+        <v>0.1980100917816162</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1738174057006836</v>
+        <v>0.1929758691787719</v>
       </c>
       <c r="O4" t="n">
-        <v>4.329153299331665</v>
+        <v>3.514742374420166</v>
       </c>
       <c r="P4" t="n">
-        <v>22.93747425079346</v>
+        <v>9.900504589080811</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.69087028503418</v>
+        <v>9.6487934589386</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250629-053019</t>
+          <t>20250724-141027</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -3996,22 +3996,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4043,56 +4043,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>57.53157567977905</v>
+        <v>226.7638430595398</v>
       </c>
       <c r="D5" t="n">
-        <v>9.770000457763672</v>
+        <v>19.42000007629395</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2880230283035951</v>
+        <v>0.5441945215403023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.5333333611488342</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3909091055393219</v>
+        <v>0.4827586114406585</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1702127605676651</v>
+        <v>0.4834123253822326</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1438848972320556</v>
+        <v>0.459330141544342</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1345064491033554</v>
+        <v>0.1478106081485748</v>
       </c>
       <c r="K5" t="n">
-        <v>78.09844493865967</v>
+        <v>81.32890796661377</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0881183147430419</v>
+        <v>0.07796385288238521</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4668604660034179</v>
+        <v>0.2057876682281494</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1726175022125244</v>
+        <v>0.1984419441223144</v>
       </c>
       <c r="O5" t="n">
-        <v>4.4059157371521</v>
+        <v>3.898192644119263</v>
       </c>
       <c r="P5" t="n">
-        <v>23.3430233001709</v>
+        <v>10.28938341140747</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.630875110626221</v>
+        <v>9.922097206115724</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250629-053358</t>
+          <t>20250724-141725</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4117,22 +4117,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4164,56 +4164,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C6" t="n">
-        <v>56.76095151901245</v>
+        <v>278.8575222492218</v>
       </c>
       <c r="D6" t="n">
-        <v>9.739999771118164</v>
+        <v>21.04999923706055</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2867211147266276</v>
+        <v>0.5350919333664147</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.625</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3842364549636841</v>
+        <v>0.343137264251709</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2312925159931183</v>
+        <v>0.25</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2666666805744171</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1290459036827087</v>
+        <v>0.145951971411705</v>
       </c>
       <c r="K6" t="n">
-        <v>78.89029288291931</v>
+        <v>80.78161239624023</v>
       </c>
       <c r="L6" t="n">
-        <v>0.087501254081726</v>
+        <v>0.06973791122436521</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4656669235229492</v>
+        <v>0.1989207506179809</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1735934400558471</v>
+        <v>0.1956952857971191</v>
       </c>
       <c r="O6" t="n">
-        <v>4.375062704086304</v>
+        <v>3.486895561218262</v>
       </c>
       <c r="P6" t="n">
-        <v>23.28334617614746</v>
+        <v>9.946037530899048</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.679672002792358</v>
+        <v>9.784764289855955</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250629-053730</t>
+          <t>20250724-142404</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>atss_resnext101</t>
+          <t>dfine_x</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -4238,22 +4238,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -4451,56 +4451,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C2" t="n">
-        <v>222.3726618289948</v>
+        <v>196.0393002033234</v>
       </c>
       <c r="D2" t="n">
-        <v>14.25</v>
+        <v>10.02000045776367</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4780287767042879</v>
+        <v>0.3174725152828075</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6315789222717285</v>
+        <v>0.2666666805744171</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6133333444595337</v>
+        <v>0.0975609719753265</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6026200652122498</v>
+        <v>0.0657894760370254</v>
       </c>
       <c r="I2" t="n">
-        <v>0.550000011920929</v>
+        <v>0.0375000014901161</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1224053874611854</v>
+        <v>0.170303463935852</v>
       </c>
       <c r="K2" t="n">
-        <v>81.77561378479004</v>
+        <v>44.52545666694641</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0823972368240356</v>
+        <v>0.0732153367996215</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2012185049057006</v>
+        <v>0.221124005317688</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1972805452346801</v>
+        <v>0.1810611724853515</v>
       </c>
       <c r="O2" t="n">
-        <v>4.119861841201782</v>
+        <v>3.660766839981079</v>
       </c>
       <c r="P2" t="n">
-        <v>10.06092524528503</v>
+        <v>11.0562002658844</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.864027261734009</v>
+        <v>9.053058624267578</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250628-110231</t>
+          <t>20250726-234221</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -4525,22 +4525,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -4572,56 +4572,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>254.9838638305664</v>
+        <v>234.8633329868317</v>
       </c>
       <c r="D3" t="n">
-        <v>14.64000034332275</v>
+        <v>9.979999542236328</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4608728053669135</v>
+        <v>0.3106387224462297</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7058823704719543</v>
+        <v>0.4545454680919647</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5198237895965576</v>
+        <v>0.3567567467689514</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4791666567325592</v>
+        <v>0.2857142984867096</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.2051282078027725</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1291781663894653</v>
+        <v>0.1707068234682083</v>
       </c>
       <c r="K3" t="n">
-        <v>75.47589492797852</v>
+        <v>50.97031307220459</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0841906023025512</v>
+        <v>0.0824490451812744</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2084130764007568</v>
+        <v>0.2182789850234985</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2022201538085937</v>
+        <v>0.1921872043609619</v>
       </c>
       <c r="O3" t="n">
-        <v>4.209530115127564</v>
+        <v>4.122452259063721</v>
       </c>
       <c r="P3" t="n">
-        <v>10.42065382003784</v>
+        <v>10.91394925117493</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.11100769042969</v>
+        <v>9.609360218048096</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250628-110905</t>
+          <t>20250726-234752</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -4646,22 +4646,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -4693,56 +4693,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>227.4099354743957</v>
+        <v>229.728419303894</v>
       </c>
       <c r="D4" t="n">
-        <v>14.22000026702881</v>
+        <v>10.40999984741211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4624636745260608</v>
+        <v>0.306918751862314</v>
       </c>
       <c r="F4" t="n">
-        <v>0.625</v>
+        <v>0.5333333611488342</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5234375</v>
+        <v>0.2956521809101105</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4742268025875091</v>
+        <v>0.2576687037944793</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4926108419895172</v>
+        <v>0.1891891956329345</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1257363110780716</v>
+        <v>0.1757416129112243</v>
       </c>
       <c r="K4" t="n">
-        <v>81.2602264881134</v>
+        <v>52.13227534294128</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0816456842422485</v>
+        <v>0.0781619262695312</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1995290613174438</v>
+        <v>0.2196516942977905</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1914499044418335</v>
+        <v>0.184062385559082</v>
       </c>
       <c r="O4" t="n">
-        <v>4.082284212112427</v>
+        <v>3.908096313476562</v>
       </c>
       <c r="P4" t="n">
-        <v>9.976453065872192</v>
+        <v>10.98258471488953</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.572495222091677</v>
+        <v>9.203119277954102</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250628-111556</t>
+          <t>20250726-235353</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -4767,22 +4767,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -4814,56 +4814,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
-        <v>242.6147477626801</v>
+        <v>174.5637443065643</v>
       </c>
       <c r="D5" t="n">
-        <v>14.27000045776367</v>
+        <v>9.720000267028809</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4791468702482455</v>
+        <v>0.3192503866942032</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7368420958518982</v>
+        <v>0.2666666805744171</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5210084319114685</v>
+        <v>0.1991701275110244</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5319148898124695</v>
+        <v>0.1742738634347915</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5235602259635925</v>
+        <v>0.1513513475656509</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1369505673646927</v>
+        <v>0.1767495274543762</v>
       </c>
       <c r="K5" t="n">
-        <v>75.41393160820007</v>
+        <v>51.16088962554932</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0741264533996582</v>
+        <v>0.075483751296997</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2068630027770996</v>
+        <v>0.2200056791305542</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2032514858245849</v>
+        <v>0.1810720252990722</v>
       </c>
       <c r="O5" t="n">
-        <v>3.70632266998291</v>
+        <v>3.774187564849854</v>
       </c>
       <c r="P5" t="n">
-        <v>10.34315013885498</v>
+        <v>11.00028395652771</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.16257429122925</v>
+        <v>9.053601264953612</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250628-112235</t>
+          <t>20250726-235950</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -4888,22 +4888,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4935,56 +4935,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>224.6367123126984</v>
+        <v>188.4336407184601</v>
       </c>
       <c r="D6" t="n">
-        <v>14.6899995803833</v>
+        <v>10.10999965667725</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4726493005951245</v>
+        <v>0.3092736005783081</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5333333611488342</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5209302306175232</v>
+        <v>0.3024390339851379</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4337349534034729</v>
+        <v>0.2962962985038757</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.2981366515159607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1360589861869812</v>
+        <v>0.1694085299968719</v>
       </c>
       <c r="K6" t="n">
-        <v>81.29399561882019</v>
+        <v>45.33633136749268</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0855302572250366</v>
+        <v>0.0721746826171875</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2059227466583252</v>
+        <v>0.2229632759094238</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1908987998962402</v>
+        <v>0.1743371152877807</v>
       </c>
       <c r="O6" t="n">
-        <v>4.276512861251831</v>
+        <v>3.608734130859375</v>
       </c>
       <c r="P6" t="n">
-        <v>10.29613733291626</v>
+        <v>11.14816379547119</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.544939994812012</v>
+        <v>8.716855764389038</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250628-112913</t>
+          <t>20250727-000500</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>dfine_x</t>
+          <t>rtdetr_101</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5009,22 +5009,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5222,56 +5222,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>278.0583446025848</v>
+        <v>96.74342703819276</v>
       </c>
       <c r="D2" t="n">
-        <v>9.449999809265137</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2855997524763408</v>
+        <v>0.1514591336250305</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4705882370471954</v>
+        <v>0.5333333611488342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.446351945400238</v>
+        <v>0.2990654110908508</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2614379227161407</v>
+        <v>0.2395209521055221</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07518796622753141</v>
+        <v>0.2545454502105713</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1417351216077804</v>
+        <v>0.0993759632110595</v>
       </c>
       <c r="K2" t="n">
-        <v>50.82845306396485</v>
+        <v>19.02056312561035</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08394699573516839</v>
+        <v>0.0526122379302978</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2276633167266845</v>
+        <v>0.0791683864593505</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1750546646118164</v>
+        <v>0.0876512956619262</v>
       </c>
       <c r="O2" t="n">
-        <v>4.197349786758423</v>
+        <v>2.630611896514893</v>
       </c>
       <c r="P2" t="n">
-        <v>11.38316583633423</v>
+        <v>3.958419322967529</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.75273323059082</v>
+        <v>4.382564783096313</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-011258</t>
+          <t>20250728-041534</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -5296,22 +5296,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -5343,56 +5343,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>176.093367099762</v>
+        <v>100.3240933418274</v>
       </c>
       <c r="D3" t="n">
-        <v>8.960000038146973</v>
+        <v>5.269999980926514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2876619489296623</v>
+        <v>0.1561820422930102</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5555555820465088</v>
+        <v>0.625</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.3606557250022888</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2967741787433624</v>
+        <v>0.1549295783042907</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2727272808551788</v>
+        <v>0.1428571492433548</v>
       </c>
       <c r="J3" t="n">
-        <v>0.139300525188446</v>
+        <v>0.08790912479162211</v>
       </c>
       <c r="K3" t="n">
-        <v>51.04634118080139</v>
+        <v>24.50573015213013</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0881639289855957</v>
+        <v>0.0442283725738525</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2220408964157104</v>
+        <v>0.07782101154327389</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1859228515625</v>
+        <v>0.0832792377471923</v>
       </c>
       <c r="O3" t="n">
-        <v>4.408196449279785</v>
+        <v>2.211418628692627</v>
       </c>
       <c r="P3" t="n">
-        <v>11.10204482078552</v>
+        <v>3.891050577163696</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.296142578125</v>
+        <v>4.163961887359619</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-011953</t>
+          <t>20250728-041829</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -5417,22 +5417,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -5464,56 +5464,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>175.0558722019196</v>
+        <v>77.53937029838562</v>
       </c>
       <c r="D4" t="n">
-        <v>9.199999809265137</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2865354645511378</v>
+        <v>0.151889724501719</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.3636363744735718</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2805429995059967</v>
+        <v>0.1194968521595001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2545454502105713</v>
+        <v>0.1190476194024086</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2769230902194977</v>
+        <v>0.1403508782386779</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1351966857910156</v>
+        <v>0.08871929347515101</v>
       </c>
       <c r="K4" t="n">
-        <v>51.62609767913818</v>
+        <v>24.53727865219116</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08691141128540029</v>
+        <v>0.0467973184585571</v>
       </c>
       <c r="M4" t="n">
-        <v>0.219960331916809</v>
+        <v>0.0775628805160522</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1828197717666626</v>
+        <v>0.0835463619232177</v>
       </c>
       <c r="O4" t="n">
-        <v>4.34557056427002</v>
+        <v>2.339865922927856</v>
       </c>
       <c r="P4" t="n">
-        <v>10.99801659584045</v>
+        <v>3.878144025802612</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.14098858833313</v>
+        <v>4.177318096160889</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-012456</t>
+          <t>20250728-042128</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -5538,22 +5538,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -5585,56 +5585,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>208.3125281333924</v>
+        <v>94.27967572212221</v>
       </c>
       <c r="D5" t="n">
-        <v>9.020000457763672</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2908859691529903</v>
+        <v>0.152111716940999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2148148119449615</v>
+        <v>0.2368421107530594</v>
       </c>
       <c r="H5" t="n">
-        <v>0.147058829665184</v>
+        <v>0.1807228922843933</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1835748851299286</v>
+        <v>0.1342281848192215</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1507403999567031</v>
+        <v>0.08734887093305579</v>
       </c>
       <c r="K5" t="n">
-        <v>51.36559915542603</v>
+        <v>24.4866509437561</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0840347480773925</v>
+        <v>0.044284176826477</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2212776088714599</v>
+        <v>0.077675814628601</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1755838441848755</v>
+        <v>0.0846240806579589</v>
       </c>
       <c r="O5" t="n">
-        <v>4.201737403869629</v>
+        <v>2.214208841323853</v>
       </c>
       <c r="P5" t="n">
-        <v>11.063880443573</v>
+        <v>3.883790731430054</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.779192209243774</v>
+        <v>4.231204032897949</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-013009</t>
+          <t>20250728-042404</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -5659,22 +5659,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -5706,56 +5706,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C6" t="n">
-        <v>163.9096109867096</v>
+        <v>100.5184051990509</v>
       </c>
       <c r="D6" t="n">
-        <v>9.220000267028809</v>
+        <v>5.599999904632568</v>
       </c>
       <c r="E6" t="n">
-        <v>0.289426326751709</v>
+        <v>0.1511137837928439</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4347825944423675</v>
+        <v>0.6000000238418579</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2377622425556183</v>
+        <v>0.3181818127632141</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1975308656692505</v>
+        <v>0.2368421107530594</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2025316506624221</v>
+        <v>0.2614379227161407</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1457934528589248</v>
+        <v>0.07669854909181591</v>
       </c>
       <c r="K6" t="n">
-        <v>51.30203032493591</v>
+        <v>18.7708830833435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0880595350265503</v>
+        <v>0.051768684387207</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2200976943969726</v>
+        <v>0.0789256477355957</v>
       </c>
       <c r="N6" t="n">
-        <v>0.188633451461792</v>
+        <v>0.0844220352172851</v>
       </c>
       <c r="O6" t="n">
-        <v>4.402976751327515</v>
+        <v>2.588434219360352</v>
       </c>
       <c r="P6" t="n">
-        <v>11.00488471984863</v>
+        <v>3.946282386779785</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.4316725730896</v>
+        <v>4.221101760864258</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-013555</t>
+          <t>20250728-042656</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_101</t>
+          <t>rtdetr_18</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -5993,56 +5993,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>79.93271207809448</v>
+        <v>152.0846362113953</v>
       </c>
       <c r="D2" t="n">
-        <v>3.220000028610229</v>
+        <v>8.119999885559082</v>
       </c>
       <c r="E2" t="n">
-        <v>0.163637346625328</v>
+        <v>0.2443662683945149</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.3529411852359772</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1749271154403686</v>
+        <v>0.2567567527294159</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1546961367130279</v>
+        <v>0.2278480976819992</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1676646769046783</v>
+        <v>0.2690058350563049</v>
       </c>
       <c r="J2" t="n">
-        <v>0.07868111878633489</v>
+        <v>0.1300392597913742</v>
       </c>
       <c r="K2" t="n">
-        <v>24.8440535068512</v>
+        <v>39.4359655380249</v>
       </c>
       <c r="L2" t="n">
-        <v>0.049770278930664</v>
+        <v>0.0584059810638427</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0789781379699707</v>
+        <v>0.1451315307617187</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0839408779144287</v>
+        <v>0.147839069366455</v>
       </c>
       <c r="O2" t="n">
-        <v>2.488513946533203</v>
+        <v>2.920299053192139</v>
       </c>
       <c r="P2" t="n">
-        <v>3.948906898498535</v>
+        <v>7.256576538085938</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.197043895721436</v>
+        <v>7.391953468322754</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250630-163309</t>
+          <t>20250729-073121</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6067,22 +6067,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6114,56 +6114,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n">
-        <v>82.94010400772095</v>
+        <v>157.1212708950043</v>
       </c>
       <c r="D3" t="n">
-        <v>3.069999933242798</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1619403860440441</v>
+        <v>0.2388198834025498</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4705882370471954</v>
+        <v>0.5882353186607361</v>
       </c>
       <c r="G3" t="n">
-        <v>0.229629635810852</v>
+        <v>0.3980582654476166</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1963190138339996</v>
+        <v>0.3804347813129425</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1973684281110763</v>
+        <v>0.3425414264202118</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0880353674292564</v>
+        <v>0.1310166418552398</v>
       </c>
       <c r="K3" t="n">
-        <v>24.64055061340332</v>
+        <v>33.2644419670105</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0504706192016601</v>
+        <v>0.0574394273757934</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0794656038284301</v>
+        <v>0.1393909502029419</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0847529792785644</v>
+        <v>0.1405654716491699</v>
       </c>
       <c r="O3" t="n">
-        <v>2.523530960083008</v>
+        <v>2.871971368789673</v>
       </c>
       <c r="P3" t="n">
-        <v>3.973280191421509</v>
+        <v>6.969547510147095</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.237648963928223</v>
+        <v>7.028273582458496</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250630-163549</t>
+          <t>20250729-073541</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6188,22 +6188,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -6235,56 +6235,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C4" t="n">
-        <v>71.94191479682922</v>
+        <v>188.8142569065094</v>
       </c>
       <c r="D4" t="n">
-        <v>3.200000047683716</v>
+        <v>7.789999961853027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1640213721177794</v>
+        <v>0.2409445598517378</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4545454680919647</v>
+        <v>0.5882353186607361</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1731601804494857</v>
+        <v>0.4423076808452606</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1372549086809158</v>
+        <v>0.4205128252506256</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1681415885686874</v>
+        <v>0.3894736766815185</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0826059728860855</v>
+        <v>0.1254096627235412</v>
       </c>
       <c r="K4" t="n">
-        <v>24.3565137386322</v>
+        <v>39.63312125205994</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0495301961898803</v>
+        <v>0.0603057718276977</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08162109375</v>
+        <v>0.140747365951538</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0913511562347412</v>
+        <v>0.1441439723968506</v>
       </c>
       <c r="O4" t="n">
-        <v>2.476509809494019</v>
+        <v>3.015288591384888</v>
       </c>
       <c r="P4" t="n">
-        <v>4.0810546875</v>
+        <v>7.037368297576904</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.567557811737061</v>
+        <v>7.207198619842529</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250630-163832</t>
+          <t>20250729-074006</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -6356,56 +6356,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>77.9242832660675</v>
+        <v>117.7288596630096</v>
       </c>
       <c r="D5" t="n">
-        <v>3.009999990463257</v>
+        <v>7.03000020980835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1625414797846151</v>
+        <v>0.2490489721991295</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.4705882370471954</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1774193495512008</v>
+        <v>0.2666666805744171</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0903225839138031</v>
+        <v>0.2681564390659332</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0155038759112358</v>
+        <v>0.2421052604913711</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08941617608070369</v>
+        <v>0.1261631995439529</v>
       </c>
       <c r="K5" t="n">
-        <v>24.21170854568481</v>
+        <v>39.50232434272766</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0488409900665283</v>
+        <v>0.057856273651123</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07839747428894039</v>
+        <v>0.1436797285079956</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08412740230560301</v>
+        <v>0.1390899133682251</v>
       </c>
       <c r="O5" t="n">
-        <v>2.442049503326416</v>
+        <v>2.892813682556152</v>
       </c>
       <c r="P5" t="n">
-        <v>3.919873714447021</v>
+        <v>7.18398642539978</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.206370115280151</v>
+        <v>6.954495668411255</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250630-164103</t>
+          <t>20250729-074504</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -6477,56 +6477,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>75.38966917991638</v>
+        <v>122.0944290161133</v>
       </c>
       <c r="D6" t="n">
-        <v>3.140000104904175</v>
+        <v>7.340000152587891</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1625669485201006</v>
+        <v>0.2421513110399246</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4545454680919647</v>
+        <v>0.4444444477558136</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1810344755649566</v>
+        <v>0.2133333384990692</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2060085833072662</v>
+        <v>0.0575539581477642</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1975308656692505</v>
+        <v>0.0601503774523735</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0766159072518348</v>
+        <v>0.1272099465131759</v>
       </c>
       <c r="K6" t="n">
-        <v>24.2958812713623</v>
+        <v>39.12742900848389</v>
       </c>
       <c r="L6" t="n">
-        <v>0.048354058265686</v>
+        <v>0.0562835645675659</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07953474044799801</v>
+        <v>0.137411847114563</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0934274673461914</v>
+        <v>0.1433889579772949</v>
       </c>
       <c r="O6" t="n">
-        <v>2.417702913284302</v>
+        <v>2.814178228378296</v>
       </c>
       <c r="P6" t="n">
-        <v>3.976737022399902</v>
+        <v>6.870592355728149</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.67137336730957</v>
+        <v>7.169447898864746</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250630-164340</t>
+          <t>20250729-074851</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_18</t>
+          <t>rtdetr_50</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6551,22 +6551,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -6764,56 +6764,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>112.4241089820862</v>
+        <v>31.4412362575531</v>
       </c>
       <c r="D2" t="n">
-        <v>7.03000020980835</v>
+        <v>10.38000011444092</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2498732710426504</v>
+        <v>0.1337848825332445</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.1900452524423599</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3209876418113708</v>
+        <v>0.1739130467176437</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2763157784938812</v>
+        <v>0.198019802570343</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1174616143107414</v>
+        <v>0.08953032642602921</v>
       </c>
       <c r="K2" t="n">
-        <v>39.27435159683228</v>
+        <v>13.92612814903259</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0719214248657226</v>
+        <v>0.0334889841079711</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1385349988937378</v>
+        <v>0.0483784627914428</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1434763813018799</v>
+        <v>0.0403045415878295</v>
       </c>
       <c r="O2" t="n">
-        <v>3.596071243286133</v>
+        <v>1.67444920539856</v>
       </c>
       <c r="P2" t="n">
-        <v>6.92674994468689</v>
+        <v>2.418923139572144</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.173819065093994</v>
+        <v>2.015227079391479</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-042532</t>
+          <t>20250730-082814</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -6823,7 +6823,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -6838,22 +6838,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -6885,56 +6885,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C3" t="n">
-        <v>144.4242517948151</v>
+        <v>49.53089809417725</v>
       </c>
       <c r="D3" t="n">
-        <v>5.980000019073486</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2453905355255558</v>
+        <v>0.1356688598170876</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4174757301807403</v>
+        <v>0.147058829665184</v>
       </c>
       <c r="H3" t="n">
-        <v>0.380952388048172</v>
+        <v>0.0933333337306976</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3517588078975677</v>
+        <v>0.0799999982118606</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1120862960815429</v>
+        <v>0.0970804020762443</v>
       </c>
       <c r="K3" t="n">
-        <v>33.56844520568848</v>
+        <v>13.76367616653442</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0665574502944946</v>
+        <v>0.0425487565994262</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1416918611526489</v>
+        <v>0.0471172666549682</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1426890611648559</v>
+        <v>0.0414147567749023</v>
       </c>
       <c r="O3" t="n">
-        <v>3.327872514724731</v>
+        <v>2.127437829971313</v>
       </c>
       <c r="P3" t="n">
-        <v>7.084593057632446</v>
+        <v>2.355863332748413</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.134453058242798</v>
+        <v>2.070737838745117</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-042915</t>
+          <t>20250730-082940</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -6959,22 +6959,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7006,56 +7006,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>119.2156474590302</v>
+        <v>59.81226134300232</v>
       </c>
       <c r="D4" t="n">
-        <v>6.679999828338623</v>
+        <v>10.40999984741211</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2479126605797897</v>
+        <v>0.1363157707301876</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.3636363744735718</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3796296417713165</v>
+        <v>0.1732283532619476</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3214285671710968</v>
+        <v>0.0699300691485405</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2709677517414093</v>
+        <v>0.0699300691485405</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1092376485466957</v>
+        <v>0.1051647588610649</v>
       </c>
       <c r="K4" t="n">
-        <v>39.17008852958679</v>
+        <v>14.06505489349365</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0705547666549682</v>
+        <v>0.0449717950820922</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1398252201080322</v>
+        <v>0.0469785118103027</v>
       </c>
       <c r="N4" t="n">
-        <v>0.150270414352417</v>
+        <v>0.0412590026855468</v>
       </c>
       <c r="O4" t="n">
-        <v>3.527738332748413</v>
+        <v>2.248589754104614</v>
       </c>
       <c r="P4" t="n">
-        <v>6.991261005401611</v>
+        <v>2.348925590515137</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.51352071762085</v>
+        <v>2.062950134277344</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-043329</t>
+          <t>20250730-083123</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7080,22 +7080,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7127,56 +7127,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="C5" t="n">
-        <v>109.3206372261047</v>
+        <v>65.93677115440369</v>
       </c>
       <c r="D5" t="n">
-        <v>6.019999980926514</v>
+        <v>10.39000034332275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2500528821891004</v>
+        <v>0.136277126462272</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4285714328289032</v>
+        <v>0.4705882370471954</v>
       </c>
       <c r="G5" t="n">
-        <v>0.290909081697464</v>
+        <v>0.2256809324026107</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2514970004558563</v>
+        <v>0.187845304608345</v>
       </c>
       <c r="I5" t="n">
-        <v>0.29347825050354</v>
+        <v>0.1787709444761276</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1170803755521774</v>
+        <v>0.1191580966114997</v>
       </c>
       <c r="K5" t="n">
-        <v>39.05071640014648</v>
+        <v>13.68471217155456</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0650611019134521</v>
+        <v>0.0480315780639648</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1398629713058471</v>
+        <v>0.0474717426300048</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1400305652618408</v>
+        <v>0.0414557886123657</v>
       </c>
       <c r="O5" t="n">
-        <v>3.253055095672607</v>
+        <v>2.401578903198242</v>
       </c>
       <c r="P5" t="n">
-        <v>6.993148565292358</v>
+        <v>2.373587131500244</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.001528263092041</v>
+        <v>2.072789430618286</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-043719</t>
+          <t>20250730-083318</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7201,22 +7201,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -7248,56 +7248,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C6" t="n">
-        <v>119.273922920227</v>
+        <v>63.52526378631592</v>
       </c>
       <c r="D6" t="n">
-        <v>6.429999828338623</v>
+        <v>10.40999984741211</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2509305362784585</v>
+        <v>0.1349828720447562</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5882353186607361</v>
+        <v>0.4166666567325592</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2945736348628998</v>
+        <v>0.3003663122653961</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2732240557670593</v>
+        <v>0.2692307829856872</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2566844820976257</v>
+        <v>0.2741116881370544</v>
       </c>
       <c r="J6" t="n">
-        <v>0.123480349779129</v>
+        <v>0.1084774285554885</v>
       </c>
       <c r="K6" t="n">
-        <v>38.97738981246948</v>
+        <v>13.56637716293335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0731889629364013</v>
+        <v>0.0451746273040771</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1389760160446167</v>
+        <v>0.0499604797363281</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1395127439498901</v>
+        <v>0.0423900365829467</v>
       </c>
       <c r="O6" t="n">
-        <v>3.659448146820069</v>
+        <v>2.258731365203857</v>
       </c>
       <c r="P6" t="n">
-        <v>6.948800802230835</v>
+        <v>2.498023986816406</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.975637197494507</v>
+        <v>2.119501829147339</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-044057</t>
+          <t>20250730-083518</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtdetr_50</t>
+          <t>ssd_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -7322,22 +7322,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -7535,56 +7535,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>35.43418741226196</v>
+        <v>45.73959493637085</v>
       </c>
       <c r="D2" t="n">
-        <v>1.679999947547913</v>
+        <v>13.57999992370606</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1063628708097067</v>
+        <v>0.2367812108535032</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3478260934352875</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2780269086360931</v>
+        <v>0.25</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2761506140232086</v>
+        <v>0.0979020968079567</v>
       </c>
       <c r="I2" t="n">
-        <v>0.27947598695755</v>
+        <v>0.0845070406794548</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0781676769256591</v>
+        <v>0.1023709550499916</v>
       </c>
       <c r="K2" t="n">
-        <v>9.505753993988035</v>
+        <v>29.608891248703</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0474673891067504</v>
+        <v>0.038877100944519</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0451368474960327</v>
+        <v>0.1306171226501465</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0655822229385376</v>
+        <v>0.0899605321884155</v>
       </c>
       <c r="O2" t="n">
-        <v>2.373369455337524</v>
+        <v>1.943855047225952</v>
       </c>
       <c r="P2" t="n">
-        <v>2.256842374801636</v>
+        <v>6.530856132507324</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.27911114692688</v>
+        <v>4.498026609420776</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250701-181539</t>
+          <t>20250731-011432</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -7609,22 +7609,22 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -7656,56 +7656,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C3" t="n">
-        <v>47.20968842506409</v>
+        <v>82.8361222743988</v>
       </c>
       <c r="D3" t="n">
-        <v>1.679999947547913</v>
+        <v>13.57999992370606</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1096394629044047</v>
+        <v>0.2370200902223587</v>
       </c>
       <c r="F3" t="n">
         <v>0.4000000059604645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3199999928474426</v>
+        <v>0.2949308753013611</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125</v>
+        <v>0.1476510018110275</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07299269735813139</v>
+        <v>0.1447368413209915</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0864223316311836</v>
+        <v>0.0903556272387504</v>
       </c>
       <c r="K3" t="n">
-        <v>9.582319736480711</v>
+        <v>29.35517311096192</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0416803693771362</v>
+        <v>0.0410943794250488</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0621651887893676</v>
+        <v>0.1233717823028564</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0560252380371093</v>
+        <v>0.0908624649047851</v>
       </c>
       <c r="O3" t="n">
-        <v>2.084018468856812</v>
+        <v>2.054718971252441</v>
       </c>
       <c r="P3" t="n">
-        <v>3.108259439468384</v>
+        <v>6.168589115142822</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.801261901855469</v>
+        <v>4.543123245239258</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250701-181713</t>
+          <t>20250731-011643</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -7730,22 +7730,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -7777,56 +7777,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>68.84328579902649</v>
+        <v>67.72021293640137</v>
       </c>
       <c r="D4" t="n">
-        <v>1.75</v>
+        <v>13.57999992370606</v>
       </c>
       <c r="E4" t="n">
-        <v>0.106232425553745</v>
+        <v>0.2365439051793793</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3199999928474426</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3366336524486542</v>
+        <v>0.0949152559041976</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3574879169464111</v>
+        <v>0.0930232554674148</v>
       </c>
       <c r="I4" t="n">
-        <v>0.377880185842514</v>
+        <v>0.0958083868026733</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08715514093637459</v>
+        <v>0.1049294248223304</v>
       </c>
       <c r="K4" t="n">
-        <v>15.13347029685974</v>
+        <v>29.49594140052796</v>
       </c>
       <c r="L4" t="n">
-        <v>0.042675986289978</v>
+        <v>0.0402000331878662</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0453265237808227</v>
+        <v>0.1315650510787963</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0572882175445556</v>
+        <v>0.09121476173400871</v>
       </c>
       <c r="O4" t="n">
-        <v>2.133799314498901</v>
+        <v>2.010001659393311</v>
       </c>
       <c r="P4" t="n">
-        <v>2.266326189041138</v>
+        <v>6.578252553939819</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.864410877227783</v>
+        <v>4.56073808670044</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250701-181853</t>
+          <t>20250731-011931</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -7851,22 +7851,22 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -7901,53 +7901,53 @@
         <v>74</v>
       </c>
       <c r="C5" t="n">
-        <v>57.87346458435059</v>
+        <v>82.54334115982056</v>
       </c>
       <c r="D5" t="n">
-        <v>1.700000047683716</v>
+        <v>13.57999992370606</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1079923895162504</v>
+        <v>0.236913371529128</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4444444477558136</v>
+        <v>0.375</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3022222220897674</v>
+        <v>0.3033707737922668</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3142857253551483</v>
+        <v>0.2543352544307709</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3304347693920135</v>
+        <v>0.2666666805744171</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0759125724434852</v>
+        <v>0.1013489887118339</v>
       </c>
       <c r="K5" t="n">
-        <v>14.80296182632446</v>
+        <v>29.52214169502258</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0415892648696899</v>
+        <v>0.0401648092269897</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0524316835403442</v>
+        <v>0.1301773166656494</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0573213958740234</v>
+        <v>0.090606689453125</v>
       </c>
       <c r="O5" t="n">
-        <v>2.079463243484497</v>
+        <v>2.008240461349488</v>
       </c>
       <c r="P5" t="n">
-        <v>2.621584177017212</v>
+        <v>6.508865833282471</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.866069793701172</v>
+        <v>4.53033447265625</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250701-182100</t>
+          <t>20250731-012204</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -7972,22 +7972,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -8019,56 +8019,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
-        <v>65.04409623146057</v>
+        <v>77.16748404502869</v>
       </c>
       <c r="D6" t="n">
-        <v>1.730000019073486</v>
+        <v>13.57999992370606</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1076468588518244</v>
+        <v>0.2362854277742082</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4705882370471954</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3495145738124847</v>
+        <v>0.3482142984867096</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3861386179924011</v>
+        <v>0.2344827651977539</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3619047701358795</v>
+        <v>0.2448979616165161</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08457668125629419</v>
+        <v>0.0942645519971847</v>
       </c>
       <c r="K6" t="n">
-        <v>9.538661479949951</v>
+        <v>29.50834608078003</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0427147769927978</v>
+        <v>0.0433912515640258</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0542079448699951</v>
+        <v>0.1227405166625976</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0570634841918945</v>
+        <v>0.0898820543289184</v>
       </c>
       <c r="O6" t="n">
-        <v>2.135738849639893</v>
+        <v>2.169562578201294</v>
       </c>
       <c r="P6" t="n">
-        <v>2.710397243499756</v>
+        <v>6.137025833129883</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.853174209594727</v>
+        <v>4.494102716445923</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250701-182256</t>
+          <t>20250731-012451</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>rtmdet_tiny</t>
+          <t>yolox_l</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.5.0dev</t>
+          <t>2.5.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>eugene/benchmark-refactor</t>
+          <t>release/2.5</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57d55ba78</t>
+          <t>ac266a23b</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -8306,56 +8306,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
-        <v>78.27259135246277</v>
+        <v>28.23449778556824</v>
       </c>
       <c r="D2" t="n">
-        <v>5.429999828338623</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1006341506171663</v>
+        <v>0.1421160864479401</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.5333333611488342</v>
       </c>
       <c r="G2" t="n">
-        <v>0.304347813129425</v>
+        <v>0.2952381074428558</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2831050157546997</v>
+        <v>0.1167883202433586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2938388586044311</v>
+        <v>0.1142857149243354</v>
       </c>
       <c r="J2" t="n">
-        <v>0.08819039165973661</v>
+        <v>0.1073194816708564</v>
       </c>
       <c r="K2" t="n">
-        <v>13.98778581619263</v>
+        <v>13.46582937240601</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0409800195693969</v>
+        <v>0.0367176055908203</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0480949687957763</v>
+        <v>0.0684329557418823</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0420356225967407</v>
+        <v>0.0857119083404541</v>
       </c>
       <c r="O2" t="n">
-        <v>2.049000978469849</v>
+        <v>1.835880279541016</v>
       </c>
       <c r="P2" t="n">
-        <v>2.404748439788818</v>
+        <v>3.421647787094116</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.101781129837036</v>
+        <v>4.285595417022705</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250702-075336</t>
+          <t>20250627-154332</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -8427,56 +8427,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C3" t="n">
-        <v>66.62251377105713</v>
+        <v>54.53179097175598</v>
       </c>
       <c r="D3" t="n">
-        <v>5.440000057220459</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0999198863480953</v>
+        <v>0.1453837430563526</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4705882370471954</v>
+        <v>0.4545454680919647</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2868525981903076</v>
+        <v>0.3453237414360046</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2189054787158966</v>
+        <v>0.1702127605676651</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2244897931814193</v>
+        <v>0.1702127605676651</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1473220735788345</v>
+        <v>0.1033629700541496</v>
       </c>
       <c r="K3" t="n">
-        <v>13.84789514541626</v>
+        <v>19.05455040931702</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0475631237030029</v>
+        <v>0.0341227149963378</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0482358264923095</v>
+        <v>0.0746825742721557</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0420561981201171</v>
+        <v>0.0817127323150634</v>
       </c>
       <c r="O3" t="n">
-        <v>2.378156185150146</v>
+        <v>1.706135749816894</v>
       </c>
       <c r="P3" t="n">
-        <v>2.411791324615479</v>
+        <v>3.734128713607788</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.10280990600586</v>
+        <v>4.085636615753174</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250702-075550</t>
+          <t>20250627-154458</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -8548,56 +8548,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C4" t="n">
-        <v>39.69147205352783</v>
+        <v>35.30303716659546</v>
       </c>
       <c r="D4" t="n">
-        <v>5.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1006532036871821</v>
+        <v>0.145390549166636</v>
       </c>
       <c r="F4" t="n">
         <v>0.4444444477558136</v>
       </c>
       <c r="G4" t="n">
-        <v>0.220095694065094</v>
+        <v>0.4064171016216278</v>
       </c>
       <c r="H4" t="n">
-        <v>0.220095694065094</v>
+        <v>0.4064171016216278</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2252252250909805</v>
+        <v>0.3777777850627899</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0876852422952652</v>
+        <v>0.1012242883443832</v>
       </c>
       <c r="K4" t="n">
-        <v>14.21025395393372</v>
+        <v>13.69968914985657</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0461113786697387</v>
+        <v>0.0343540620803833</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0482138967514038</v>
+        <v>0.0705648183822631</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0419540500640869</v>
+        <v>0.0880775594711303</v>
       </c>
       <c r="O4" t="n">
-        <v>2.305568933486938</v>
+        <v>1.717703104019165</v>
       </c>
       <c r="P4" t="n">
-        <v>2.41069483757019</v>
+        <v>3.528240919113159</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.097702503204346</v>
+        <v>4.403877973556519</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250702-075751</t>
+          <t>20250627-154700</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -8669,56 +8669,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
-        <v>56.13003754615784</v>
+        <v>24.30372500419617</v>
       </c>
       <c r="D5" t="n">
-        <v>5.349999904632568</v>
+        <v>6.480000019073486</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0990127591958528</v>
+        <v>0.1450734102520449</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3529411852359772</v>
+        <v>0.4285714328289032</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2254545390605926</v>
+        <v>0.2285714298486709</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1666666716337204</v>
+        <v>0.1678321659564972</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1656804680824279</v>
+        <v>0.1655172407627105</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1085607782006263</v>
+        <v>0.1123669892549514</v>
       </c>
       <c r="K5" t="n">
-        <v>14.02350425720215</v>
+        <v>13.50382041931152</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0482001876831054</v>
+        <v>0.0391898775100708</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0486549806594848</v>
+        <v>0.06975539684295649</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0422198009490966</v>
+        <v>0.0855686616897583</v>
       </c>
       <c r="O5" t="n">
-        <v>2.410009384155273</v>
+        <v>1.95949387550354</v>
       </c>
       <c r="P5" t="n">
-        <v>2.432749032974243</v>
+        <v>3.487769842147827</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.110990047454834</v>
+        <v>4.278433084487915</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250702-075926</t>
+          <t>20250627-154833</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -8790,56 +8790,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="C6" t="n">
-        <v>78.23798227310181</v>
+        <v>48.95585107803345</v>
       </c>
       <c r="D6" t="n">
-        <v>5.349999904632568</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="E6" t="n">
-        <v>0.10108359554492</v>
+        <v>0.1430299766361712</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4210526347160339</v>
+        <v>0.5555555820465088</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2521008551120758</v>
+        <v>0.4036697149276733</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2380952388048172</v>
+        <v>0.409090906381607</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2278480976819992</v>
+        <v>0.3856502175331116</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1061934307217598</v>
+        <v>0.1071620285511016</v>
       </c>
       <c r="K6" t="n">
-        <v>13.99969840049744</v>
+        <v>13.50362253189087</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0424557876586914</v>
+        <v>0.0353055238723754</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0486385583877563</v>
+        <v>0.0782226800918579</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0424478244781494</v>
+        <v>0.0870033740997314</v>
       </c>
       <c r="O6" t="n">
-        <v>2.12278938293457</v>
+        <v>1.765276193618774</v>
       </c>
       <c r="P6" t="n">
-        <v>2.431927919387817</v>
+        <v>3.911134004592896</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.122391223907471</v>
+        <v>4.350168704986572</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250702-080118</t>
+          <t>20250627-154955</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ssd_mobilenetv2</t>
+          <t>atss_mobilenetv2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -9077,56 +9077,56 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C2" t="n">
-        <v>42.1855309009552</v>
+        <v>35.43418741226196</v>
       </c>
       <c r="D2" t="n">
-        <v>7.46999979019165</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1561978249213634</v>
+        <v>0.1063628708097067</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4000000059604645</v>
+        <v>0.3478260934352875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2513661086559295</v>
+        <v>0.2780269086360931</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2395209521055221</v>
+        <v>0.2761506140232086</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2196531742811203</v>
+        <v>0.27947598695755</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0868712589144706</v>
+        <v>0.0781676769256591</v>
       </c>
       <c r="K2" t="n">
-        <v>24.24160218238831</v>
+        <v>9.505753993988035</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0607024955749511</v>
+        <v>0.0474673891067504</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1243903017044067</v>
+        <v>0.0451368474960327</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0910670518875122</v>
+        <v>0.0655822229385376</v>
       </c>
       <c r="O2" t="n">
-        <v>3.035124778747559</v>
+        <v>2.373369455337524</v>
       </c>
       <c r="P2" t="n">
-        <v>6.219515085220337</v>
+        <v>2.256842374801636</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.55335259437561</v>
+        <v>3.27911114692688</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>20250703-095742</t>
+          <t>20250701-181539</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -9198,56 +9198,56 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>56.21379971504211</v>
+        <v>47.20968842506409</v>
       </c>
       <c r="D3" t="n">
-        <v>7.46999979019165</v>
+        <v>1.679999947547913</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1562094834667664</v>
+        <v>0.1096394629044047</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4705882370471954</v>
+        <v>0.4000000059604645</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1818181872367859</v>
+        <v>0.3199999928474426</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1538461595773697</v>
+        <v>0.125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1558441519737243</v>
+        <v>0.07299269735813139</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0757221058011055</v>
+        <v>0.0864223316311836</v>
       </c>
       <c r="K3" t="n">
-        <v>24.37872648239136</v>
+        <v>9.582319736480711</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0602682304382324</v>
+        <v>0.0416803693771362</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1270966100692749</v>
+        <v>0.0621651887893676</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09271280765533441</v>
+        <v>0.0560252380371093</v>
       </c>
       <c r="O3" t="n">
-        <v>3.013411521911621</v>
+        <v>2.084018468856812</v>
       </c>
       <c r="P3" t="n">
-        <v>6.354830503463745</v>
+        <v>3.108259439468384</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.635640382766724</v>
+        <v>2.801261901855469</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>20250703-095951</t>
+          <t>20250701-181713</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -9319,56 +9319,56 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C4" t="n">
-        <v>82.51090264320374</v>
+        <v>68.84328579902649</v>
       </c>
       <c r="D4" t="n">
-        <v>7.440000057220459</v>
+        <v>1.75</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1563284798890729</v>
+        <v>0.106232425553745</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4705882370471954</v>
+        <v>0.3199999928474426</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2010050266981125</v>
+        <v>0.3366336524486542</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1927710771560669</v>
+        <v>0.3574879169464111</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1879194676876068</v>
+        <v>0.377880185842514</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0903817266225814</v>
+        <v>0.08715514093637459</v>
       </c>
       <c r="K4" t="n">
-        <v>29.38321471214294</v>
+        <v>15.13347029685974</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0547609949111938</v>
+        <v>0.042675986289978</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1250140428543091</v>
+        <v>0.0453265237808227</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0917749309539795</v>
+        <v>0.0572882175445556</v>
       </c>
       <c r="O4" t="n">
-        <v>2.738049745559692</v>
+        <v>2.133799314498901</v>
       </c>
       <c r="P4" t="n">
-        <v>6.250702142715454</v>
+        <v>2.266326189041138</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.588746547698975</v>
+        <v>2.864410877227783</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20250703-100215</t>
+          <t>20250701-181853</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -9440,56 +9440,56 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C5" t="n">
-        <v>59.30970430374146</v>
+        <v>57.87346458435059</v>
       </c>
       <c r="D5" t="n">
-        <v>7.46999979019165</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1577946129772398</v>
+        <v>0.1079923895162504</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4166666567325592</v>
+        <v>0.4444444477558136</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1382113844156265</v>
+        <v>0.3022222220897674</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1530054658651352</v>
+        <v>0.3142857253551483</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1494252830743789</v>
+        <v>0.3304347693920135</v>
       </c>
       <c r="J5" t="n">
-        <v>0.075857937335968</v>
+        <v>0.0759125724434852</v>
       </c>
       <c r="K5" t="n">
-        <v>29.59560465812683</v>
+        <v>14.80296182632446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0524991369247436</v>
+        <v>0.0415892648696899</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1313894271850585</v>
+        <v>0.0524316835403442</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0910916900634765</v>
+        <v>0.0573213958740234</v>
       </c>
       <c r="O5" t="n">
-        <v>2.624956846237183</v>
+        <v>2.079463243484497</v>
       </c>
       <c r="P5" t="n">
-        <v>6.56947135925293</v>
+        <v>2.621584177017212</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.554584503173828</v>
+        <v>2.866069793701172</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>20250703-100504</t>
+          <t>20250701-182100</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -9561,56 +9561,56 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C6" t="n">
-        <v>64.09513258934021</v>
+        <v>65.04409623146057</v>
       </c>
       <c r="D6" t="n">
-        <v>7.46999979019165</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1565769951222306</v>
+        <v>0.1076468588518244</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.4705882370471954</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2307692319154739</v>
+        <v>0.3495145738124847</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1955555528402328</v>
+        <v>0.3861386179924011</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2026431709527969</v>
+        <v>0.3619047701358795</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0753964111208915</v>
+        <v>0.08457668125629419</v>
       </c>
       <c r="K6" t="n">
-        <v>29.37168312072754</v>
+        <v>9.538661479949951</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0531354141235351</v>
+        <v>0.0427147769927978</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1303678941726684</v>
+        <v>0.0542079448699951</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0927859115600586</v>
+        <v>0.0570634841918945</v>
       </c>
       <c r="O6" t="n">
-        <v>2.656770706176758</v>
+        <v>2.135738849639893</v>
       </c>
       <c r="P6" t="n">
-        <v>6.518394708633423</v>
+        <v>2.710397243499756</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.63929557800293</v>
+        <v>2.853174209594727</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>20250703-100731</t>
+          <t>20250701-182256</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -9620,7 +9620,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>yolox_l</t>
+          <t>rtmdet_tiny</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
